--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>销售合同</t>
   </si>
@@ -107,99 +107,103 @@
     <t>日期：</t>
   </si>
   <si>
+    <t>{secondSignDate}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{companyTaxpayerId}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{sellerName}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{sellerTelNumber}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{companyAddress}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>规格型号</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>合计：</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民币大写：</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{totalQty}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{totalTaxAmount}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{chineseAmount}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.no}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.productName}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.declareModel}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.qty}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.unit}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.taxAmount}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{customerName}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{customerName}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{company}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{company}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>{firstSignDate}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>{secondSignDate}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{companyTaxpayerId}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{sellerName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{sellerTelNumber}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{companyAddress}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>规格型号</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>合计：</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>人民币大写：</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{totalQty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{totalTaxAmount}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{chineseAmount}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.no}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.declareModel}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.qty}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.unit}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.taxPrice}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.taxAmount}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{customerName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{customerName}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{company}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>{company}</t>
+    <t>{firstSignDate}</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -686,15 +690,17 @@
       <c r="G5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="H5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="3"/>
@@ -702,7 +708,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I6" s="15"/>
     </row>
@@ -719,7 +725,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="10"/>
     </row>
@@ -736,7 +742,7 @@
         <v>8</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" s="10"/>
     </row>
@@ -753,7 +759,7 @@
         <v>10</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" s="10"/>
     </row>
@@ -770,7 +776,7 @@
         <v>12</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="16"/>
     </row>
@@ -799,7 +805,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>19</v>
@@ -816,49 +822,49 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="11"/>
       <c r="E17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.15">
@@ -1168,13 +1174,13 @@
         <v>24</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>5</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.15">
@@ -1182,34 +1188,34 @@
         <v>25</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:H4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A20:H49"/>
-    <mergeCell ref="A1:H4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="H9:I9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,27 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$H$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$J$25</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>销售合同</t>
   </si>
@@ -108,6 +121,12 @@
     <t>单位</t>
   </si>
   <si>
+    <t>单价</t>
+  </si>
+  <si>
+    <t>金额合计</t>
+  </si>
+  <si>
     <t>单价（含税）</t>
   </si>
   <si>
@@ -132,6 +151,12 @@
     <t>{.unit}</t>
   </si>
   <si>
+    <t>{.price}</t>
+  </si>
+  <si>
+    <t>{.amount}</t>
+  </si>
+  <si>
     <t>{.taxPrice}</t>
   </si>
   <si>
@@ -142,6 +167,9 @@
   </si>
   <si>
     <t>{totalQty}</t>
+  </si>
+  <si>
+    <t>{.totalAmount}</t>
   </si>
   <si>
     <t>{totalTaxAmount}</t>
@@ -179,7 +207,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -219,69 +247,33 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF2A14FC"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF2A14FC"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -326,6 +318,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -371,7 +378,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,49 +414,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,121 +552,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -622,21 +650,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -665,6 +678,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -721,148 +749,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -894,88 +922,88 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1282,20 +1310,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="50.5" customWidth="1"/>
     <col min="4" max="4" width="18.75" customWidth="1"/>
-    <col min="5" max="5" width="15.75" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="7" width="16.375" customWidth="1"/>
-    <col min="8" max="8" width="19.875" customWidth="1"/>
+    <col min="5" max="7" width="15.75" customWidth="1"/>
+    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="16.375" customWidth="1"/>
+    <col min="10" max="10" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" customHeight="1" spans="1:8">
+    <row r="1" ht="51" customHeight="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1306,8 +1334,10 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-    </row>
-    <row r="2" customFormat="1" ht="15" customHeight="1" spans="1:8">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" customFormat="1" ht="15" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1316,8 +1346,10 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1334,8 +1366,10 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1352,8 +1386,10 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
@@ -1370,8 +1406,10 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
@@ -1388,8 +1426,10 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -1406,9 +1446,11 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="9"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1425,8 +1467,10 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-    </row>
-    <row r="9" ht="24.75" customHeight="1" spans="1:8">
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" ht="24.75" customHeight="1" spans="1:10">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1435,8 +1479,10 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:8">
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:10">
       <c r="A10" s="9" t="s">
         <v>21</v>
       </c>
@@ -1447,9 +1493,11 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
-    </row>
-    <row r="11" ht="16" customHeight="1" spans="1:8">
-      <c r="A11" s="11" t="s">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" ht="16" customHeight="1" spans="1:10">
+      <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="8"/>
@@ -1459,8 +1507,10 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -1469,144 +1519,164 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:8">
-      <c r="A13" s="12" t="s">
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:10">
+      <c r="A13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" ht="17" customHeight="1" spans="1:8">
-      <c r="A14" s="15" t="s">
+      <c r="I13" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="J13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="15" t="s">
+    </row>
+    <row r="14" ht="31" customHeight="1" spans="1:10">
+      <c r="A14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="B14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="D14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="E14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="F14" s="12" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:8">
-      <c r="A15" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="12" t="s">
+      <c r="H14" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="19" t="s">
+      <c r="I14" s="12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="1:8">
-      <c r="A16" s="12" t="s">
+      <c r="J14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="20" t="s">
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:10">
+      <c r="A15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:10">
+      <c r="A16" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
     </row>
     <row r="18" ht="107" customHeight="1" spans="1:1">
-      <c r="A18" s="21" t="s">
-        <v>44</v>
+      <c r="A18" s="18" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="107" customHeight="1"/>
     <row r="20" ht="107" customHeight="1"/>
     <row r="21" ht="107" customHeight="1"/>
-    <row r="24" ht="22.5" customHeight="1" spans="1:8">
-      <c r="A24" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="23" t="s">
+    <row r="24" ht="22.5" customHeight="1" spans="1:10">
+      <c r="A24" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="I24" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="J24" s="20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1" spans="1:8">
-      <c r="A25" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="23" t="s">
+    <row r="25" ht="30" customHeight="1" spans="1:10">
+      <c r="A25" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>47</v>
+      <c r="I25" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E3:J3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E5:J5"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E6:J6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E7:J7"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E8:J8"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A18:H21"/>
+    <mergeCell ref="A18:J21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.156944444444444" right="0.118055555555556" top="0.354166666666667" bottom="0.393055555555556" header="0.275" footer="0.298611111111111"/>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -169,7 +169,7 @@
     <t>{totalQty}</t>
   </si>
   <si>
-    <t>{.totalAmount}</t>
+    <t>{totalAmount}</t>
   </si>
   <si>
     <t>{totalTaxAmount}</t>
@@ -1318,7 +1318,7 @@
     <col min="3" max="3" width="50.5" customWidth="1"/>
     <col min="4" max="4" width="18.75" customWidth="1"/>
     <col min="5" max="7" width="15.75" customWidth="1"/>
-    <col min="8" max="8" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="14.875" customWidth="1"/>
     <col min="9" max="9" width="16.375" customWidth="1"/>
     <col min="10" max="10" width="19.875" customWidth="1"/>
   </cols>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -127,7 +127,7 @@
     <t>金额合计</t>
   </si>
   <si>
-    <t>单价（含税）</t>
+    <t>含税单价</t>
   </si>
   <si>
     <t>价税合计</t>
@@ -894,7 +894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -916,6 +916,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1448,182 +1451,182 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="9"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="8"/>
       <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" ht="24.75" customHeight="1" spans="1:10">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:10">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
     </row>
     <row r="11" ht="16" customHeight="1" spans="1:10">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:10">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="23" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" ht="31" customHeight="1" spans="1:10">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:10">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="11" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11" t="s">
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="23" t="s">
+      <c r="I15" s="18"/>
+      <c r="J15" s="24" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:10">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="16" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
     </row>
     <row r="18" ht="107" customHeight="1" spans="1:1">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1631,30 +1634,30 @@
     <row r="20" ht="107" customHeight="1"/>
     <row r="21" ht="107" customHeight="1"/>
     <row r="24" ht="22.5" customHeight="1" spans="1:10">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="19" t="s">
+      <c r="I24" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="21" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:10">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="19" t="s">
+      <c r="I25" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="J25" s="20" t="s">
+      <c r="J25" s="21" t="s">
         <v>52</v>
       </c>
     </row>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -124,13 +124,13 @@
     <t>单价</t>
   </si>
   <si>
-    <t>金额合计</t>
+    <t>合计未税金额</t>
   </si>
   <si>
     <t>含税单价</t>
   </si>
   <si>
-    <t>价税合计</t>
+    <t>合计含税金额</t>
   </si>
   <si>
     <t>{.no}</t>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -124,13 +124,13 @@
     <t>单价</t>
   </si>
   <si>
-    <t>合计未税金额</t>
+    <t>金额合计</t>
   </si>
   <si>
     <t>含税单价</t>
   </si>
   <si>
-    <t>合计含税金额</t>
+    <t>价税合计</t>
   </si>
   <si>
     <t>{.no}</t>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -185,9 +185,9 @@
 本合同经双方协商签订如下协议:
 一、货物质量承诺：乙方提供的货物需符合：中华人民共和国国家标准；货物生产商的产品质量标准；符合产品说明书表明的质量状况和使用性能。
 二、发货方式：乙方收到甲方确认购销合同后，乙方在承诺三个工作日内发货至甲方国内指定收货地址（如特殊情况下出现库存不足，乙方提前三个工作日通知甲方，告知具体出货时间)。
-三、收货条款：甲方或甲方指定客户在收到已方产品当时，应在现场检查产品数量、规格型号及外观，如有差错、短缺或损坏，甲方或甲方指定客户应当即向运输或快递公司当场提出索赔申诉，同时2个工作日内书面告知甲方；如未按时书面通知的，视为甲方收到乙方产品合格并验收入库。
+三、收货条款：甲方或甲方指定客户在收到乙方产品当时，应在现场检查产品数量、规格型号及外观，如有差错、短缺或损坏，甲方或甲方指定客户应当即向运输或快递公司当场提出索赔申诉，同时2个工作日内书面告知甲方；如未按时书面通知的，视为甲方收到乙方产品合格并验收入库。
 四、付款方式：付款至乙方指定收款账户，收到订单后先支付100%货款后安排发货。
-五、售后服务承诺：甲方负责授权销售渠道及平台的客户售后服务工作，乙方为甲方的售后服务提供技术咨询支持；乙方对售出产品提供一年保质期，从验收合格当天开始计算（如未通知乙方的验货结果，则默认合格）。在保质期内，如产品在正常工作下发生故障或者破损，甲方将免费对产品提供换货或维修服务，运费由甲方负责。如由于人为或者是操作不当或自然损耗／灾害而产生的故障，乙方不负责换货和维修。
+五、售后服务承诺：甲方负责授权销售渠道及平台的客户售后服务工作，乙方为甲方的售后服务提供技术咨询支持；乙方对售出产品提供一年保质期，从验收合格当天开始计算（如未通知乙方的验货结果，则默认合格）。在保质期内，如产品在正常工作下发生故障或者破损，乙方将免费对产品提供换货或维修服务，运费由乙方负责。如由于人为或者是操作不当或自然损耗／灾害而产生的故障，乙方不负责换货和维修。
 六、订单取消与变更：甲方若要取消或变更订单，需要在原交期前至少7个工作日书面通知乙方，经乙方同意后才可以取消或变更订单。因甲方需求分批发货的订单，如甲方超过3个月不提提货需求，则乙方有权按合同收取尾款，但不收甲方仓储管理费。乙方专门为甲方定制的产品订单，一经双方书面确认后不得取消或变更。
 七、退换货规定 ：除产品质量等特殊原因外，乙方发货后，甲方一律不得退货；因乙方产品质量原因或发错货，在中国境内运费由乙方承担；因甲方选型、误用、滥用，无理由拒收等原因导致的破损而退换货，运费由甲方承担；
 八、因甲方原因延迟支付货款（乙方允许欠款情况除外），乙方有权解除合同并主张甲方完好退还已收到的乙方货物，返还货物运费由甲方承担，并要求甲方支付违约金（按照订单金额的5%收取）。

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -181,15 +181,15 @@
     <t>{chineseAmount}</t>
   </si>
   <si>
-    <t>本合同一式贰份，甲乙双方各持壹份，经双方盖章后每份具有同等效力。有关本合同的任何修改应当经过甲乙双方签字盖章确认
+    <t>本合同一式贰份，甲乙双方各持壹份，经双方盖章后每份具有同等效力。有关本合同的任何修改应当经过甲乙双方盖章确认
 本合同经双方协商签订如下协议:
 一、货物质量承诺：乙方提供的货物需符合：中华人民共和国国家标准；货物生产商的产品质量标准；符合产品说明书表明的质量状况和使用性能。
 二、发货方式：乙方收到甲方确认购销合同后，乙方在承诺三个工作日内发货至甲方国内指定收货地址（如特殊情况下出现库存不足，乙方提前三个工作日通知甲方，告知具体出货时间)。
-三、收货条款：甲方或甲方指定客户在收到乙方产品当时，应在现场检查产品数量、规格型号及外观，如有差错、短缺或损坏，甲方或甲方指定客户应当即向运输或快递公司当场提出索赔申诉，同时2个工作日内书面告知甲方；如未按时书面通知的，视为甲方收到乙方产品合格并验收入库。
+三、收货条款：甲方或甲方指定客户在收到乙方产品当时，应在现场检查产品数量、规格型号及外观，如有差错、短缺或损坏，甲方或甲方指定客户应当即向运输或快递公司当场提出索赔申诉，告知乙方；如未按时书面通知的，视为甲方及甲方指定客户收到乙方产品合格并验收入库。
 四、付款方式：付款至乙方指定收款账户，收到订单后先支付100%货款后安排发货。
 五、售后服务承诺：甲方负责授权销售渠道及平台的客户售后服务工作，乙方为甲方的售后服务提供技术咨询支持；乙方对售出产品提供一年保质期，从验收合格当天开始计算（如未通知乙方的验货结果，则默认合格）。在保质期内，如产品在正常工作下发生故障或者破损，乙方将免费对产品提供换货或维修服务，运费由乙方负责。如由于人为或者是操作不当或自然损耗／灾害而产生的故障，乙方不负责换货和维修。
-六、订单取消与变更：甲方若要取消或变更订单，需要在原交期前至少7个工作日书面通知乙方，经乙方同意后才可以取消或变更订单。因甲方需求分批发货的订单，如甲方超过3个月不提提货需求，则乙方有权按合同收取尾款，但不收甲方仓储管理费。乙方专门为甲方定制的产品订单，一经双方书面确认后不得取消或变更。
-七、退换货规定 ：除产品质量等特殊原因外，乙方发货后，甲方一律不得退货；因乙方产品质量原因或发错货，在中国境内运费由乙方承担；因甲方选型、误用、滥用，无理由拒收等原因导致的破损而退换货，运费由甲方承担；
+六、订单取消与变更：甲方若要取消或变更订单，需要在原交期前至少7个工作日书面通知乙方，经乙方同意后才可以取消或变更订单。因甲方需求分批发货的订单，如甲方超过3个月不按照提货需求进行提货的，则乙方有权按合同收取尾款，但不收甲方仓储管理费。乙方专门为甲方定制的产品订单，一经双方书面确认后不得取消或变更。
+七、退换货规定 ：除产品质量等特殊原因外，乙方发货后，甲方一律不得退货；因乙方产品质量原因或发错货，在中国境内运费由乙方承担；
 八、因甲方原因延迟支付货款（乙方允许欠款情况除外），乙方有权解除合同并主张甲方完好退还已收到的乙方货物，返还货物运费由甲方承担，并要求甲方支付违约金（按照订单金额的5%收取）。
 九、因本合同而产生的一切纠纷应甲乙双方友好协商解决，协商不成的，由乙方所在地人民法院管辖。本合同自双方签订加盖公章之日起即生效，双方终止合同需要另行签署书面协议或以函件进行确认。
 十、甲乙双方应当保守商业机密，就本合同履行过程中产生的所有信息（包括但不限于商品成本价、销售价、本合同及附件本身等）以及双方的商业机密承担保密义务，亦不得用于除本合同目的以外的其他用途。</t>

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoContract.xlsx
@@ -185,7 +185,7 @@
 本合同经双方协商签订如下协议:
 一、货物质量承诺：乙方提供的货物需符合：中华人民共和国国家标准；货物生产商的产品质量标准；符合产品说明书表明的质量状况和使用性能。
 二、发货方式：乙方收到甲方确认购销合同后，乙方在承诺三个工作日内发货至甲方国内指定收货地址（如特殊情况下出现库存不足，乙方提前三个工作日通知甲方，告知具体出货时间)。
-三、收货条款：甲方或甲方指定客户在收到乙方产品当时，应在现场检查产品数量、规格型号及外观，如有差错、短缺或损坏，甲方或甲方指定客户应当即向运输或快递公司当场提出索赔申诉，告知乙方；如未按时书面通知的，视为甲方及甲方指定客户收到乙方产品合格并验收入库。
+三、收货条款：甲方或甲方指定客户在收到乙方产品当时，应在现场检查产品数量、规格型号及外观，如有差错、短缺或损坏，甲方或甲方指定客户应当即向运输或快递公司当场提出索赔申诉，同时2个工作日内书面告知乙方；如未按时书面通知的，视为甲方及甲方指定客户收到乙方产品合格并验收入库。
 四、付款方式：付款至乙方指定收款账户，收到订单后先支付100%货款后安排发货。
 五、售后服务承诺：甲方负责授权销售渠道及平台的客户售后服务工作，乙方为甲方的售后服务提供技术咨询支持；乙方对售出产品提供一年保质期，从验收合格当天开始计算（如未通知乙方的验货结果，则默认合格）。在保质期内，如产品在正常工作下发生故障或者破损，乙方将免费对产品提供换货或维修服务，运费由乙方负责。如由于人为或者是操作不当或自然损耗／灾害而产生的故障，乙方不负责换货和维修。
 六、订单取消与变更：甲方若要取消或变更订单，需要在原交期前至少7个工作日书面通知乙方，经乙方同意后才可以取消或变更订单。因甲方需求分批发货的订单，如甲方超过3个月不按照提货需求进行提货的，则乙方有权按合同收取尾款，但不收甲方仓储管理费。乙方专门为甲方定制的产品订单，一经双方书面确认后不得取消或变更。
@@ -247,15 +247,15 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF2A14FC"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -918,16 +918,22 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -936,10 +942,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -948,15 +957,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1326,7 +1326,7 @@
     <col min="10" max="10" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" customHeight="1" spans="1:10">
+    <row r="1" ht="51" customHeight="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1340,7 +1340,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" customFormat="1" ht="15" customHeight="1" spans="1:10">
+    <row r="2" customFormat="1" ht="15" customHeight="1" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1352,7 +1352,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1392,7 +1392,7 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
     </row>
-    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
@@ -1412,7 +1412,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
@@ -1451,47 +1451,47 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="10"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:10">
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:11">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="8"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" ht="24.75" customHeight="1" spans="1:10">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:10">
-      <c r="A10" s="10" t="s">
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" ht="24.75" customHeight="1" spans="1:11">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:11">
+      <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -1499,33 +1499,33 @@
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
     </row>
-    <row r="11" ht="16" customHeight="1" spans="1:10">
-      <c r="A11" s="10" t="s">
+    <row r="11" ht="16" customHeight="1" spans="1:11">
+      <c r="A11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:10">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:11">
       <c r="A13" s="12" t="s">
         <v>23</v>
       </c>
@@ -1550,52 +1550,52 @@
       <c r="H13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" ht="31" customHeight="1" spans="1:10">
-      <c r="A14" s="13" t="s">
+    <row r="14" ht="31" customHeight="1" spans="1:11">
+      <c r="A14" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1" spans="1:10">
+    <row r="15" ht="18" customHeight="1" spans="1:11">
       <c r="A15" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="12"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
       <c r="E15" s="12" t="s">
         <v>44</v>
       </c>
@@ -1604,29 +1604,29 @@
       <c r="H15" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="18"/>
-      <c r="J15" s="24" t="s">
+      <c r="I15" s="19"/>
+      <c r="J15" s="20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1" spans="1:10">
+    <row r="16" ht="22" customHeight="1" spans="1:11">
       <c r="A16" s="12" t="s">
         <v>47</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
-    </row>
-    <row r="18" ht="107" customHeight="1" spans="1:1">
-      <c r="A18" s="19" t="s">
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+    </row>
+    <row r="18" ht="107" customHeight="1" spans="1:10">
+      <c r="A18" s="22" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1634,30 +1634,30 @@
     <row r="20" ht="107" customHeight="1"/>
     <row r="21" ht="107" customHeight="1"/>
     <row r="24" ht="22.5" customHeight="1" spans="1:10">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="21" t="s">
+      <c r="J24" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:10">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="20" t="s">
+      <c r="I25" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="J25" s="21" t="s">
+      <c r="J25" s="24" t="s">
         <v>52</v>
       </c>
     </row>
